--- a/order_template.xlsx
+++ b/order_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leon/Documents/研究室/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903AFA87-46BD-2A49-952D-4D3258CADFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4721775E-D103-344F-81D2-BF6274431B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27740" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,6 +129,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
   <fonts count="3">
     <font>
       <sz val="12"/>
@@ -177,7 +180,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -189,6 +192,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,6 +517,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -517,16 +527,23 @@
       <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="H1"/>
     </row>
     <row r="2" spans="1:8">
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="E2" s="4"/>
+      <c r="H2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>11</v>
       </c>
+      <c r="H3"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="H4"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">

--- a/order_template.xlsx
+++ b/order_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leon/Documents/研究室/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leon/Documents/研究室/04-河内研立ち上げ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4721775E-D103-344F-81D2-BF6274431B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A41BB3-D540-824C-B1E0-BA598B755AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="27740" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="27700" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>依頼者</t>
     <rPh sb="0" eb="3">
@@ -45,13 +45,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>業者</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">ギョウシャ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>メーカー</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -87,16 +80,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>依頼者：</t>
-    <rPh sb="0" eb="2">
-      <t xml:space="preserve">イライビ </t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t xml:space="preserve">シャ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>依頼日：</t>
     <rPh sb="0" eb="1">
       <t xml:space="preserve">イライビ </t>
@@ -122,6 +105,13 @@
   </si>
   <si>
     <t>以下について、ご手配のほどよろしくお願いいたします。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宛名：</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">アテナ </t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -516,29 +506,30 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H1"/>
     </row>
     <row r="2" spans="1:8">
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4"/>
       <c r="H2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3"/>
     </row>
@@ -565,10 +556,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/order_template.xlsx
+++ b/order_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/leon/Documents/研究室/04-河内研立ち上げ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A41BB3-D540-824C-B1E0-BA598B755AFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA47EE0-A2FE-CF4A-9DB7-D129DF90F2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="27700" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
+    <workbookView xWindow="-80" yWindow="620" windowWidth="27700" windowHeight="17380" xr2:uid="{785139EF-8D00-FF4B-85E1-59D800A03D9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -119,8 +119,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_ &quot;¥&quot;* #,##0_ ;_ &quot;¥&quot;* \-#,##0_ ;_ &quot;¥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -170,7 +171,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,6 +188,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -506,8 +513,9 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
-    <col min="3" max="3" width="26.28515625" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="6"/>
     <col min="8" max="8" width="10.7109375" style="5"/>
   </cols>
   <sheetData>
@@ -518,6 +526,7 @@
       <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="G1"/>
       <c r="H1"/>
     </row>
     <row r="2" spans="1:8">
@@ -525,15 +534,20 @@
         <v>6</v>
       </c>
       <c r="E2" s="4"/>
+      <c r="G2"/>
       <c r="H2"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>9</v>
       </c>
+      <c r="D3"/>
+      <c r="G3"/>
       <c r="H3"/>
     </row>
     <row r="4" spans="1:8">
+      <c r="D4"/>
+      <c r="G4"/>
       <c r="H4"/>
     </row>
     <row r="5" spans="1:8">
